--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -766,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -781,7 +781,7 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -790,7 +790,7 @@
         <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
@@ -805,7 +805,7 @@
         <v>2.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
         <v>2.12</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>19</v>
@@ -850,7 +850,7 @@
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL2" t="n">
         <v>26</v>
@@ -871,10 +871,10 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>18</v>
@@ -910,7 +910,7 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H5" t="n">
         <v>3.45</v>
@@ -1351,10 +1351,10 @@
         <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1.25</v>
@@ -2739,7 +2739,7 @@
         <v>1.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
         <v>2.08</v>
@@ -2775,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>14.5</v>
@@ -2814,10 +2814,10 @@
         <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>2.26</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>3.7</v>
@@ -3118,7 +3118,7 @@
         <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
         <v>14.5</v>
@@ -3175,10 +3175,10 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>48</v>
@@ -3208,7 +3208,7 @@
         <v>13.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -3217,16 +3217,16 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB14" t="n">
         <v>50</v>
@@ -3235,7 +3235,7 @@
         <v>30</v>
       </c>
       <c r="BD14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
         <v>60</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -787,13 +787,13 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S2" t="n">
         <v>2.28</v>
@@ -802,13 +802,13 @@
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X2" t="n">
         <v>30</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -832,10 +832,10 @@
         <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -847,7 +847,7 @@
         <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>17.5</v>
@@ -859,7 +859,7 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
@@ -871,25 +871,25 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
@@ -898,10 +898,10 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
         <v>14.5</v>
@@ -910,17 +910,17 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
         <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="n">
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>5.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>5.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2503,23 +2503,23 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.35</v>
       </c>
-      <c r="G11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J12" t="n">
         <v>11.5</v>
@@ -2733,10 +2733,10 @@
         <v>1.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
@@ -2754,7 +2754,7 @@
         <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2769,7 +2769,7 @@
         <v>32</v>
       </c>
       <c r="AD12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2814,7 +2814,7 @@
         <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="AT12" t="n">
         <v>17</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3139,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
         <v>14.5</v>
@@ -3157,19 +3157,19 @@
         <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>36</v>
@@ -3202,13 +3202,13 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT14" t="n">
         <v>13.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -3217,38 +3217,38 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
         <v>30</v>
       </c>
       <c r="BD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE14" t="n">
         <v>38</v>
       </c>
-      <c r="BE14" t="n">
-        <v>60</v>
-      </c>
       <c r="BF14" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BG14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -805,19 +805,19 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -829,40 +829,40 @@
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK2" t="n">
         <v>17</v>
       </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AL2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -871,56 +871,56 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
         <v>5.2</v>
@@ -963,10 +963,10 @@
         <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>5.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>3.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
         <v>2.48</v>
@@ -2515,10 +2515,10 @@
         <v>2.84</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>1.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
         <v>11.5</v>
@@ -2733,10 +2733,10 @@
         <v>1.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
@@ -2805,7 +2805,7 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AQ12" t="n">
         <v>36</v>
@@ -2820,7 +2820,7 @@
         <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>32</v>
@@ -2835,7 +2835,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>42</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Jagiellonia Bialystock</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,37 +3076,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3127,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,310 +3139,504 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-04 06:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Real Cartagena</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Orsomarso</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>1.01</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>1000</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>1.01</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>1000</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>1.01</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1000</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>1.01</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-04 04:51:44</t>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J2" t="n">
         <v>4.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
         <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.68</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
@@ -805,13 +805,13 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
         <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
@@ -820,7 +820,7 @@
         <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
         <v>14.5</v>
@@ -832,40 +832,40 @@
         <v>18</v>
       </c>
       <c r="AE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI2" t="n">
         <v>42</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>40</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
@@ -874,13 +874,13 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
         <v>15.5</v>
@@ -901,7 +901,7 @@
         <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -910,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>6.8</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="H4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.42</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,54 +1519,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.74</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q6" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.12</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.45</v>
+        <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>1.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,61 +2688,61 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mgladbach</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="G12" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2751,123 +2751,123 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>2.42</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,66 +3265,66 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mgladbach</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.55</v>
+        <v>1.15</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>1.16</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>19.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.26</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,310 +3333,892 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>260</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT15" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AU15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
+      <c r="BD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG15" t="n">
         <v>48</v>
       </c>
-      <c r="AM15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Real Cartagena</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Orsomarso</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-03-04 06:59:45</t>
+      <c r="F19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,16 +766,16 @@
         <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -787,25 +787,25 @@
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
         <v>2.12</v>
@@ -814,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -832,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>15</v>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -856,71 +856,71 @@
         <v>26</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>36</v>
-      </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1151,19 +1151,19 @@
         <v>1.34</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
         <v>5.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1178,7 +1178,7 @@
         <v>2.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
         <v>1.6</v>
@@ -1187,13 +1187,13 @@
         <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
         <v>3.9</v>
@@ -1247,68 +1247,68 @@
         <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AO4" t="n">
         <v>290</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="n">
-        <v>80</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>130</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BA4" t="n">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
         <v>3.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>170</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
         <v>11</v>
@@ -1357,16 +1357,16 @@
         <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
@@ -1375,141 +1375,141 @@
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT6" t="n">
         <v>7.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Van Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="G8" t="n">
-        <v>1.12</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>17.5</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>17.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -3076,28 +3076,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,61 +3270,61 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mgladbach</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>2.76</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="I16" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,66 +3653,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mgladbach</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>1.16</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>19.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.87</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.71</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC17" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="BD17" t="n">
         <v>20</v>
       </c>
-      <c r="AX17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>26</v>
-      </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BF17" t="n">
-        <v>22</v>
+        <v>2.28</v>
       </c>
       <c r="BG17" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Jagiellonia Bialystock</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>2.74</v>
       </c>
       <c r="H18" t="n">
-        <v>1.99</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -4041,184 +4041,572 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Real Cartagena</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Orsomarso</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="F21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.67</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>4.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>3.3</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K21" t="n">
         <v>5.3</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-04 09:11:02</t>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
         <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
@@ -787,25 +787,25 @@
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
         <v>2.12</v>
@@ -814,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -832,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>15</v>
@@ -844,10 +844,10 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>17.5</v>
@@ -856,71 +856,71 @@
         <v>26</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
         <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -951,70 +951,70 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M3" t="n">
         <v>1.02</v>
       </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AB3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>2.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1205,110 +1205,110 @@
         <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
         <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
         <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4</v>
       </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
         <v>3.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
@@ -1378,7 +1378,7 @@
         <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1462,7 +1462,7 @@
         <v>3.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
         <v>3.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1572,7 +1572,7 @@
         <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
@@ -1650,7 +1650,7 @@
         <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
@@ -1674,13 +1674,13 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
         <v>4.6</v>
@@ -1692,11 +1692,11 @@
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.71</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
@@ -1739,165 +1739,165 @@
         <v>7.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Van Buyuksehir Belediyespor</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.73</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>2.72</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Van Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>17.5</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>1.07</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2882,25 +2882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.16</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,61 +3658,61 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mgladbach</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.16</v>
+        <v>1.68</v>
       </c>
       <c r="H17" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>1.31</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>2.78</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Mgladbach</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>1.15</v>
       </c>
       <c r="H19" t="n">
-        <v>1.99</v>
+        <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>2.46</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>2.84</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>4.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,42 +4235,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Jagiellonia Bialystock</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.55</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,310 +4303,698 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-04 13:28:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-04 13:28:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Real Cartagena</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Orsomarso</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>1.45</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G23" t="n">
         <v>1.67</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H23" t="n">
         <v>4.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>3.3</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K23" t="n">
         <v>5.3</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-03-04 11:19:42</t>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,10 +763,10 @@
         <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
@@ -775,7 +775,7 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -799,13 +799,13 @@
         <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
         <v>2.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
         <v>2.12</v>
@@ -859,7 +859,7 @@
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J3" t="n">
         <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
         <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1011,7 +1011,7 @@
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA3" t="n">
         <v>10.5</v>
@@ -1059,62 +1059,62 @@
         <v>4.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J4" t="n">
         <v>5.8</v>
@@ -1163,64 +1163,64 @@
         <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y4" t="n">
         <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE4" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
@@ -1229,13 +1229,13 @@
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
         <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1250,65 +1250,65 @@
         <v>5.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
         <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1387,34 +1387,34 @@
         <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
@@ -1423,16 +1423,16 @@
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>40</v>
@@ -1441,19 +1441,19 @@
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
@@ -1465,44 +1465,44 @@
         <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>3.15</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="BA5" t="n">
         <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
@@ -1551,10 +1551,10 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.35</v>
@@ -1569,7 +1569,7 @@
         <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
@@ -1584,7 +1584,7 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X6" t="n">
         <v>15.5</v>
@@ -1641,7 +1641,7 @@
         <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>11.5</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dukla Banska Bystrica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>MSK Povazska Bystrica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
+        <v>140</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT7" t="n">
         <v>7.2</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AU7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV7" t="n">
         <v>20</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AW7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="BC7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BD7" t="n">
-        <v>1.54</v>
+        <v>25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.54</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Prostejov</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zizkov</t>
+          <t>Samorin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>2.72</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,129 +1969,129 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AR8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>13</v>
       </c>
-      <c r="AE8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BA8" t="n">
-        <v>1.35</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.35</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.35</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.37</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Pribram</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vysocina Jihlava</t>
+          <t>Tatran Lip Mikulas</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Van Buyuksehir Belediyespor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.73</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="V10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.2</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>St Polten</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Rapid Vienna (Am)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="G12" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>SK Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.3</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.65</v>
-      </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>First Vienna Fc 1894</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.8</v>
       </c>
-      <c r="I14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FC Liefering</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Bregenz</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Akritas Chlorakas</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.16</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.42</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>8.199999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H18" t="n">
         <v>3.15</v>
       </c>
-      <c r="G18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mgladbach</t>
+          <t>Van Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.15</v>
+        <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>1.65</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4121,111 +4121,111 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,30 +4235,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="H20" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="J20" t="n">
         <v>3.55</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>German Bundesliga 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.6</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>22</v>
       </c>
-      <c r="AF21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17</v>
-      </c>
       <c r="AI21" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>46</v>
       </c>
       <c r="AM21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>2.68</v>
       </c>
       <c r="AQ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>23</v>
-      </c>
       <c r="AY21" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>30</v>
+        <v>3.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>50</v>
+        <v>2.92</v>
       </c>
       <c r="BC21" t="n">
-        <v>32</v>
+        <v>2.88</v>
       </c>
       <c r="BD21" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="BE21" t="n">
-        <v>60</v>
+        <v>3.25</v>
       </c>
       <c r="BF21" t="n">
-        <v>29</v>
+        <v>3.25</v>
       </c>
       <c r="BG21" t="n">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,3482 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>HB Koge</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G22" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="I22" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2</v>
+      </c>
+      <c r="X23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aarhus Fremad</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kolding IF</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Hobro</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Viktoria Koln</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1860 Munich</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Al-Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Al-Hazm (KSA)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Al-Taawoun Buraidah</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al-Fateh (KSA)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Al Najma Club</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>34</v>
+      </c>
+      <c r="J30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Al Ittihad (EGY)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ismaily</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>German Bundesliga</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mgladbach</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" t="n">
+        <v>21</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" t="n">
+        <v>13</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>12</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Polish I Liga</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Stal Mielec</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GKS Tychy</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Real Cartagena</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Orsomarso</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F39" t="n">
         <v>1.45</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G39" t="n">
         <v>1.67</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H39" t="n">
         <v>4.7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I39" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J39" t="n">
         <v>3.3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K39" t="n">
         <v>5.3</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q39" t="n">
         <v>1.79</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-03-04 13:28:42</t>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH79"/>
+  <dimension ref="A1:BH80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -808,13 +808,13 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -871,7 +871,7 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
         <v>11.5</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
@@ -996,7 +996,7 @@
         <v>2.46</v>
       </c>
       <c r="U3" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
         <v>4.4</v>
@@ -1062,7 +1062,7 @@
         <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AR3" t="n">
         <v>3.15</v>
@@ -1098,7 +1098,7 @@
         <v>5.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1175,28 +1175,28 @@
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
@@ -1208,7 +1208,7 @@
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
@@ -1217,19 +1217,19 @@
         <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="n">
         <v>170</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>140</v>
@@ -1250,43 +1250,43 @@
         <v>5.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>65</v>
       </c>
       <c r="BB4" t="n">
         <v>9.6</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF4" t="n">
         <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1357,7 +1357,7 @@
         <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1378,19 +1378,19 @@
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1477,13 +1477,13 @@
         <v>3.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
         <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1572,7 +1572,7 @@
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1766,7 +1766,7 @@
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1933,13 +1933,13 @@
         <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1954,31 +1954,31 @@
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
         <v>15.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
         <v>38</v>
@@ -2032,7 +2032,7 @@
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>5.1</v>
@@ -2059,10 +2059,10 @@
         <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>19.5</v>
@@ -2074,17 +2074,17 @@
         <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>19.5</v>
+        <v>980</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.3</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
@@ -2754,7 +2754,7 @@
         <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
         <v>55</v>
@@ -2793,7 +2793,7 @@
         <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM12" t="n">
         <v>180</v>
@@ -2805,16 +2805,16 @@
         <v>150</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2823,7 +2823,7 @@
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AW12" t="n">
         <v>4.2</v>
@@ -2835,32 +2835,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BA12" t="n">
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BD12" t="n">
         <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="BG12" t="n">
         <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3032,19 +3032,19 @@
         <v>5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BC13" t="n">
         <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
         <v>5.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.42</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H14" t="n">
         <v>7.2</v>
@@ -3109,7 +3109,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
@@ -3136,7 +3136,7 @@
         <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
         <v>4.6</v>
@@ -3330,7 +3330,7 @@
         <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.85</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,22 +3691,22 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="O17" t="n">
         <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.78</v>
       </c>
       <c r="I19" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
         <v>2.92</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
         <v>2.84</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
         <v>4.1</v>
@@ -4264,7 +4264,7 @@
         <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -4273,16 +4273,16 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.36</v>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R20" t="n">
         <v>1.23</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="V23" t="n">
         <v>1.3</v>
@@ -4909,10 +4909,10 @@
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>980</v>
@@ -4924,7 +4924,7 @@
         <v>980</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL23" t="n">
         <v>980</v>
@@ -4933,7 +4933,7 @@
         <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO23" t="n">
         <v>65</v>
@@ -4945,10 +4945,10 @@
         <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
         <v>7.8</v>
@@ -4960,7 +4960,7 @@
         <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF23" t="n">
         <v>12</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX24" t="n">
         <v>13.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
         <v>4.3</v>
@@ -5234,7 +5234,7 @@
         <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5455,10 +5455,10 @@
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V26" t="n">
         <v>1.36</v>
@@ -5557,7 +5557,7 @@
         <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H27" t="n">
         <v>4.1</v>
@@ -5637,10 +5637,10 @@
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>1.32</v>
@@ -5658,52 +5658,52 @@
         <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X27" t="n">
         <v>15.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
         <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG27" t="n">
         <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
         <v>130</v>
@@ -5721,13 +5721,13 @@
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
@@ -5736,7 +5736,7 @@
         <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
         <v>19</v>
@@ -5757,20 +5757,20 @@
         <v>18</v>
       </c>
       <c r="BD27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O28" t="n">
         <v>1.25</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G29" t="n">
         <v>3.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I29" t="n">
         <v>2.72</v>
@@ -6019,22 +6019,22 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="T29" t="n">
         <v>1.55</v>
@@ -6043,7 +6043,7 @@
         <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W29" t="n">
         <v>1.48</v>
@@ -6052,7 +6052,7 @@
         <v>980</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
         <v>980</v>
@@ -6061,7 +6061,7 @@
         <v>980</v>
       </c>
       <c r="AB29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC29" t="n">
         <v>10.5</v>
@@ -6070,7 +6070,7 @@
         <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
         <v>980</v>
@@ -6085,80 +6085,80 @@
         <v>980</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
         <v>980</v>
       </c>
       <c r="AM29" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN29" t="n">
         <v>980</v>
       </c>
       <c r="AO29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP29" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT29" t="n">
         <v>10</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
         <v>3.5</v>
       </c>
       <c r="BA29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD29" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.95</v>
       </c>
       <c r="BE29" t="n">
         <v>4</v>
       </c>
       <c r="BF29" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG29" t="n">
         <v>13</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
         <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -6234,7 +6234,7 @@
         <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V30" t="n">
         <v>1.9</v>
@@ -6300,7 +6300,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AR30" t="n">
         <v>2.36</v>
@@ -6318,31 +6318,31 @@
         <v>2.28</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AX30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AY30" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AZ30" t="n">
         <v>2.42</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BB30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BD30" t="n">
         <v>2.58</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BF30" t="n">
         <v>2.68</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
         <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
@@ -6431,10 +6431,10 @@
         <v>1.8</v>
       </c>
       <c r="V31" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>12.5</v>
@@ -6494,7 +6494,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
         <v>8.199999999999999</v>
@@ -6506,10 +6506,10 @@
         <v>11</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
         <v>18</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>4.7</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="G32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H32" t="n">
         <v>2.18</v>
@@ -6604,13 +6604,13 @@
         <v>1.02</v>
       </c>
       <c r="O32" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
         <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G33" t="n">
         <v>3.8</v>
@@ -6780,7 +6780,7 @@
         <v>2.24</v>
       </c>
       <c r="I33" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="J33" t="n">
         <v>3.15</v>
@@ -6798,7 +6798,7 @@
         <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.74</v>
@@ -6822,7 +6822,7 @@
         <v>1.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -7183,16 +7183,16 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O35" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
         <v>1.69</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H37" t="n">
         <v>3.85</v>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>3.45</v>
@@ -7580,13 +7580,13 @@
         <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="R37" t="n">
         <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T37" t="n">
         <v>1.66</v>
@@ -7598,7 +7598,7 @@
         <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X37" t="n">
         <v>17.5</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="AL37" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM37" t="n">
         <v>130</v>
@@ -7655,62 +7655,62 @@
         <v>70</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ37" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU37" t="n">
         <v>7.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BA37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD37" t="n">
         <v>4</v>
       </c>
-      <c r="BB37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG37" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>4</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G38" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="H38" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="J38" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,34 +7765,34 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.04</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="R38" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S38" t="n">
         <v>1.47</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U38" t="n">
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>2.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
         <v>11.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE40" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AF40" t="n">
         <v>16</v>
@@ -8225,7 +8225,7 @@
         <v>23</v>
       </c>
       <c r="AL40" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AM40" t="n">
         <v>95</v>
@@ -8234,7 +8234,7 @@
         <v>11</v>
       </c>
       <c r="AO40" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AP40" t="n">
         <v>16.5</v>
@@ -8243,10 +8243,10 @@
         <v>15.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT40" t="n">
         <v>9.4</v>
@@ -8258,7 +8258,7 @@
         <v>14.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -8267,19 +8267,19 @@
         <v>9</v>
       </c>
       <c r="AZ40" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BC40" t="n">
         <v>15.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE40" t="n">
         <v>4.6</v>
@@ -8288,11 +8288,11 @@
         <v>7.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
         <v>2.14</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R41" t="n">
         <v>1.45</v>
@@ -8365,10 +8365,10 @@
         <v>2.78</v>
       </c>
       <c r="T41" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U41" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V41" t="n">
         <v>1.31</v>
@@ -8380,13 +8380,13 @@
         <v>20</v>
       </c>
       <c r="Y41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AA41" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="n">
         <v>13</v>
@@ -8440,7 +8440,7 @@
         <v>25</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT41" t="n">
         <v>9.4</v>
@@ -8464,7 +8464,7 @@
         <v>14</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB41" t="n">
         <v>19</v>
@@ -8473,7 +8473,7 @@
         <v>16.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE41" t="n">
         <v>6.4</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="O42" t="n">
         <v>1.35</v>
@@ -8562,7 +8562,7 @@
         <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V42" t="n">
         <v>1.5</v>
@@ -8610,7 +8610,7 @@
         <v>65</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL42" t="n">
         <v>70</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AR42" t="n">
         <v>12.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AT42" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU42" t="n">
         <v>2.18</v>
       </c>
-      <c r="AU42" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AV42" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="BB42" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
         <v>3.95</v>
@@ -8762,7 +8762,7 @@
         <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
         <v>4.2</v>
       </c>
       <c r="T44" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="U44" t="n">
         <v>1.92</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -9090,55 +9090,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FC Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="G45" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="H45" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="I45" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N45" t="n">
         <v>1.03</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.56</v>
-      </c>
       <c r="O45" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P45" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="R45" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -9147,10 +9147,10 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W45" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -9293,19 +9293,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G46" t="n">
         <v>3.3</v>
       </c>
       <c r="H46" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I46" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J46" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="K46" t="n">
         <v>3.4</v>
@@ -9314,25 +9314,25 @@
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>1.67</v>
       </c>
       <c r="O46" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P46" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q46" t="n">
         <v>2.24</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S46" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T46" t="n">
         <v>1.89</v>
@@ -9344,7 +9344,7 @@
         <v>1.52</v>
       </c>
       <c r="W46" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X46" t="n">
         <v>12.5</v>
@@ -9356,7 +9356,7 @@
         <v>980</v>
       </c>
       <c r="AA46" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AB46" t="n">
         <v>12</v>
@@ -9401,19 +9401,19 @@
         <v>980</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AU46" t="n">
         <v>6.2</v>
@@ -9422,41 +9422,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY46" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB46" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF46" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG46" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U47" t="n">
         <v>2.22</v>
@@ -9550,7 +9550,7 @@
         <v>14.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AB47" t="n">
         <v>17</v>
@@ -9580,16 +9580,16 @@
         <v>75</v>
       </c>
       <c r="AK47" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AL47" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AM47" t="n">
         <v>85</v>
       </c>
       <c r="AN47" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AO47" t="n">
         <v>14</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -9672,56 +9672,56 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>FC Eindhoven</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="G48" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="H48" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="I48" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N48" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="O48" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="P48" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S48" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.75</v>
-      </c>
       <c r="T48" t="n">
         <v>1.01</v>
       </c>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="W48" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,14 +9844,14 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9866,179 +9866,179 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV Maastricht</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.9</v>
+        <v>1.46</v>
       </c>
       <c r="G49" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.8</v>
       </c>
-      <c r="H49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K49" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N49" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="O49" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="P49" t="n">
-        <v>1.59</v>
+        <v>2.62</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="R49" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="S49" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="T49" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.76</v>
+        <v>1.12</v>
       </c>
       <c r="W49" t="n">
-        <v>1.27</v>
+        <v>2.8</v>
       </c>
       <c r="X49" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -10060,179 +10060,179 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MVV Maastricht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="G50" t="n">
-        <v>1.58</v>
+        <v>2.66</v>
       </c>
       <c r="H50" t="n">
-        <v>6.4</v>
+        <v>2.68</v>
       </c>
       <c r="I50" t="n">
-        <v>8.800000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="J50" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="K50" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="O50" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P50" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R50" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S50" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V50" t="n">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="W50" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -10254,186 +10254,186 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VVV Venlo</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W51" t="n">
         <v>2.38</v>
       </c>
-      <c r="G51" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.6</v>
-      </c>
       <c r="X51" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10448,179 +10448,179 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="G52" t="n">
-        <v>1.62</v>
+        <v>4.8</v>
       </c>
       <c r="H52" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>2.32</v>
       </c>
       <c r="J52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE52" t="n">
         <v>5</v>
       </c>
-      <c r="K52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W52" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -10690,10 +10690,10 @@
         <v>1.55</v>
       </c>
       <c r="S53" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T53" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="U53" t="n">
         <v>2.36</v>
@@ -10705,7 +10705,7 @@
         <v>1.28</v>
       </c>
       <c r="X53" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="Y53" t="n">
         <v>13</v>
@@ -10729,7 +10729,7 @@
         <v>18.5</v>
       </c>
       <c r="AF53" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AG53" t="n">
         <v>18</v>
@@ -10738,22 +10738,22 @@
         <v>17</v>
       </c>
       <c r="AI53" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AJ53" t="n">
         <v>85</v>
       </c>
       <c r="AK53" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AL53" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM53" t="n">
         <v>70</v>
       </c>
       <c r="AN53" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AO53" t="n">
         <v>9.4</v>
@@ -10810,11 +10810,11 @@
         <v>7.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
         <v>17.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT54" t="n">
         <v>7.6</v>
@@ -10986,16 +10986,16 @@
         <v>17.5</v>
       </c>
       <c r="BA54" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB54" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>7.4</v>
       </c>
       <c r="BC54" t="n">
         <v>21</v>
       </c>
       <c r="BD54" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE54" t="n">
         <v>9</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -11045,10 +11045,10 @@
         <v>2.84</v>
       </c>
       <c r="H55" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>3.65</v>
@@ -11087,10 +11087,10 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
         <v>2.16</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R56" t="n">
         <v>1.46</v>
@@ -11362,7 +11362,7 @@
         <v>11</v>
       </c>
       <c r="AW56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX56" t="n">
         <v>16</v>
@@ -11380,7 +11380,7 @@
         <v>4.6</v>
       </c>
       <c r="BC56" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD56" t="n">
         <v>4.6</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G57" t="n">
         <v>1.64</v>
@@ -11436,10 +11436,10 @@
         <v>7.8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J57" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K57" t="n">
         <v>4.4</v>
@@ -11451,7 +11451,7 @@
         <v>1.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O57" t="n">
         <v>1.43</v>
@@ -11460,7 +11460,7 @@
         <v>1.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R57" t="n">
         <v>1.22</v>
@@ -11478,13 +11478,13 @@
         <v>1.11</v>
       </c>
       <c r="W57" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X57" t="n">
         <v>12</v>
       </c>
       <c r="Y57" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="Z57" t="n">
         <v>75</v>
@@ -11496,31 +11496,31 @@
         <v>6</v>
       </c>
       <c r="AC57" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD57" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AE57" t="n">
         <v>220</v>
       </c>
       <c r="AF57" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG57" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH57" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AI57" t="n">
         <v>220</v>
       </c>
       <c r="AJ57" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AK57" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AL57" t="n">
         <v>65</v>
@@ -11529,7 +11529,7 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
@@ -11547,7 +11547,7 @@
         <v>9.6</v>
       </c>
       <c r="AT57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU57" t="n">
         <v>8</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
         <v>2.7</v>
       </c>
       <c r="K58" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,10 +11645,10 @@
         <v>1.15</v>
       </c>
       <c r="N58" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O58" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P58" t="n">
         <v>1.41</v>
@@ -11666,7 +11666,7 @@
         <v>2.26</v>
       </c>
       <c r="U58" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V58" t="n">
         <v>1.53</v>
@@ -11741,7 +11741,7 @@
         <v>7.4</v>
       </c>
       <c r="AT58" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU58" t="n">
         <v>6</v>
@@ -11756,7 +11756,7 @@
         <v>19</v>
       </c>
       <c r="AY58" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ58" t="n">
         <v>23</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
         <v>2.44</v>
       </c>
       <c r="U59" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V59" t="n">
         <v>1.14</v>
@@ -11887,7 +11887,7 @@
         <v>970</v>
       </c>
       <c r="AD59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE59" t="n">
         <v>230</v>
@@ -11899,7 +11899,7 @@
         <v>970</v>
       </c>
       <c r="AH59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI59" t="n">
         <v>230</v>
@@ -11926,13 +11926,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ59" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR59" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AT59" t="n">
         <v>5</v>
@@ -11941,44 +11941,44 @@
         <v>7.6</v>
       </c>
       <c r="AV59" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW59" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX59" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY59" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ59" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA59" t="n">
-        <v>8</v>
+        <v>2.48</v>
       </c>
       <c r="BB59" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC59" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD59" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE59" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BF59" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG59" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
         <v>1.16</v>
       </c>
       <c r="H60" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I60" t="n">
         <v>21</v>
@@ -12024,7 +12024,7 @@
         <v>11.5</v>
       </c>
       <c r="K60" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="L60" t="n">
         <v>1.16</v>
@@ -12051,7 +12051,7 @@
         <v>1.64</v>
       </c>
       <c r="T60" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U60" t="n">
         <v>2.08</v>
@@ -12063,13 +12063,13 @@
         <v>7.2</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="n">
         <v>1000</v>
       </c>
       <c r="Z60" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
         <v>1000</v>
@@ -12084,7 +12084,7 @@
         <v>75</v>
       </c>
       <c r="AE60" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AF60" t="n">
         <v>12</v>
@@ -12126,13 +12126,13 @@
         <v>48</v>
       </c>
       <c r="AS60" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="AT60" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU60" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AV60" t="n">
         <v>32</v>
@@ -12172,14 +12172,14 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12194,179 +12194,179 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="G61" t="n">
-        <v>2.54</v>
+        <v>1.59</v>
       </c>
       <c r="H61" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="L61" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="U61" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="V61" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ61" t="n">
         <v>14</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AK61" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP61" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z61" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE61" t="n">
+      <c r="AQ61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA61" t="n">
         <v>44</v>
       </c>
-      <c r="AF61" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG61" t="n">
+      <c r="BB61" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH61" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO61" t="n">
+      <c r="BC61" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE61" t="n">
         <v>48</v>
       </c>
-      <c r="AP61" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF61" t="n">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>6.6</v>
+        <v>95</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -12397,22 +12397,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="H62" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="I62" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="J62" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -12421,34 +12421,34 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="O62" t="n">
         <v>1.27</v>
       </c>
       <c r="P62" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R62" t="n">
         <v>1.21</v>
       </c>
       <c r="S62" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V62" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="W62" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,14 +12560,14 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12582,179 +12582,179 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G63" t="n">
-        <v>1.59</v>
+        <v>2.54</v>
       </c>
       <c r="H63" t="n">
-        <v>7.6</v>
+        <v>3.15</v>
       </c>
       <c r="I63" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="K63" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M63" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P63" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T63" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="U63" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X63" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG63" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y63" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC63" t="n">
+      <c r="AH63" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ63" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD63" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK63" t="n">
+      <c r="AR63" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>29</v>
       </c>
       <c r="AS63" t="n">
         <v>50</v>
       </c>
       <c r="AT63" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU63" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU63" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV63" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AW63" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="AX63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA63" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY63" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>42</v>
-      </c>
       <c r="BB63" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC63" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BD63" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE63" t="n">
-        <v>48</v>
+        <v>7.4</v>
       </c>
       <c r="BF63" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="BG63" t="n">
-        <v>95</v>
+        <v>6.6</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <v>2.7</v>
       </c>
       <c r="H64" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I64" t="n">
         <v>4.5</v>
@@ -12800,7 +12800,7 @@
         <v>3</v>
       </c>
       <c r="K64" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -12970,31 +12970,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="G65" t="n">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="H65" t="n">
-        <v>1.63</v>
+        <v>2.36</v>
       </c>
       <c r="I65" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="J65" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="K65" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,22 +13003,22 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="O65" t="n">
         <v>1.31</v>
       </c>
       <c r="P65" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="R65" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -13027,10 +13027,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.94</v>
+        <v>1.42</v>
       </c>
       <c r="W65" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -13164,31 +13164,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="H66" t="n">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="I66" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="J66" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K66" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13197,22 +13197,22 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="O66" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P66" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="R66" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S66" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -13221,10 +13221,10 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="W66" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="X66" t="n">
         <v>1000</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v>8.4</v>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>6.2</v>
@@ -13406,7 +13406,7 @@
         <v>2.06</v>
       </c>
       <c r="S67" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T67" t="n">
         <v>1.62</v>
@@ -13418,7 +13418,7 @@
         <v>1.12</v>
       </c>
       <c r="W67" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X67" t="n">
         <v>48</v>
@@ -13478,7 +13478,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AR67" t="n">
         <v>16</v>
@@ -13493,7 +13493,7 @@
         <v>14.5</v>
       </c>
       <c r="AV67" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW67" t="n">
         <v>16</v>
@@ -13508,7 +13508,7 @@
         <v>19</v>
       </c>
       <c r="BA67" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB67" t="n">
         <v>12</v>
@@ -13520,17 +13520,17 @@
         <v>20</v>
       </c>
       <c r="BE67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF67" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG67" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
         <v>1.66</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R70" t="n">
         <v>1.2</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
         <v>3.8</v>
       </c>
       <c r="L71" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M71" t="n">
         <v>1.09</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
         <v>1.38</v>
       </c>
       <c r="X72" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y72" t="n">
         <v>11.5</v>
@@ -14421,7 +14421,7 @@
         <v>14.5</v>
       </c>
       <c r="AH72" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI72" t="n">
         <v>34</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
         <v>5.3</v>
       </c>
       <c r="J73" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K73" t="n">
         <v>3.95</v>
@@ -14573,7 +14573,7 @@
         <v>3.55</v>
       </c>
       <c r="T73" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="U73" t="n">
         <v>1.99</v>
@@ -14645,7 +14645,7 @@
         <v>14.5</v>
       </c>
       <c r="AR73" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AS73" t="n">
         <v>10.5</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -14922,16 +14922,16 @@
         <v>1.73</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H75" t="n">
         <v>1.09</v>
       </c>
       <c r="I75" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="K75" t="n">
         <v>4.1</v>
@@ -14940,10 +14940,10 @@
         <v>1.01</v>
       </c>
       <c r="M75" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N75" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O75" t="n">
         <v>1.48</v>
@@ -14958,7 +14958,7 @@
         <v>1.2</v>
       </c>
       <c r="S75" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="T75" t="n">
         <v>2.2</v>
@@ -14970,7 +14970,7 @@
         <v>1.15</v>
       </c>
       <c r="W75" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X75" t="n">
         <v>970</v>
@@ -14985,7 +14985,7 @@
         <v>1000</v>
       </c>
       <c r="AB75" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC75" t="n">
         <v>970</v>
@@ -15027,62 +15027,62 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="AR75" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AS75" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC75" t="n">
         <v>3.5</v>
       </c>
-      <c r="AT75" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB75" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BD75" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BE75" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BF75" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BG75" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="O76" t="n">
         <v>1.3</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15328,7 @@
         <v>1.01</v>
       </c>
       <c r="M77" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N77" t="n">
         <v>2.88</v>
@@ -15349,10 +15349,10 @@
         <v>4.7</v>
       </c>
       <c r="T77" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U77" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V77" t="n">
         <v>1.37</v>
@@ -15466,18 +15466,18 @@
         <v>4.3</v>
       </c>
       <c r="BG77" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15492,373 +15492,567 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.45</v>
+        <v>2.58</v>
       </c>
       <c r="G78" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="H78" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="I78" t="n">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K78" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P78" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11</v>
+      </c>
+      <c r="I79" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K79" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W79" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Chilean Primera Division</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Deportes Concepcion</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Nublense</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G79" t="n">
+      <c r="F80" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I80" t="n">
         <v>3.05</v>
       </c>
-      <c r="H79" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I79" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J79" t="n">
+      <c r="J80" t="n">
         <v>3.3</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
+      <c r="K80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N80" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="O80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q80" t="n">
         <v>2.26</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH79" t="inlineStr">
-        <is>
-          <t>2026-03-04 20:04:18</t>
+      <c r="R80" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
@@ -787,7 +787,7 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
@@ -796,7 +796,7 @@
         <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.57</v>
@@ -808,7 +808,7 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>2.46</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
         <v>9.800000000000001</v>
@@ -1163,7 +1163,7 @@
         <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1178,7 +1178,7 @@
         <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
         <v>1.6</v>
@@ -1187,16 +1187,16 @@
         <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
@@ -1208,7 +1208,7 @@
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
@@ -1250,13 +1250,13 @@
         <v>5.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP4" t="n">
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR4" t="n">
         <v>5.7</v>
@@ -1268,7 +1268,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AV4" t="n">
         <v>30</v>
@@ -1283,10 +1283,10 @@
         <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB4" t="n">
         <v>9.6</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
         <v>5.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
         <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -1357,31 +1357,31 @@
         <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
         <v>1.84</v>
@@ -1390,7 +1390,7 @@
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1402,7 +1402,7 @@
         <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1432,7 +1432,7 @@
         <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>980</v>
@@ -1441,68 +1441,68 @@
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AX5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="BC5" t="n">
         <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
         <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1942,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
         <v>3.35</v>
@@ -1963,7 +1963,7 @@
         <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.97</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
@@ -2730,7 +2730,7 @@
         <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -2739,10 +2739,10 @@
         <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
         <v>1.19</v>
@@ -2832,7 +2832,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>3.85</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
         <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2939,10 +2939,10 @@
         <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
         <v>980</v>
@@ -2999,62 +2999,62 @@
         <v>980</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>4.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AV13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
         <v>1.58</v>
@@ -3127,7 +3127,7 @@
         <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
@@ -3324,13 +3324,13 @@
         <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
         <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3497,16 +3497,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
         <v>1.79</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3691,28 +3691,28 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
         <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
         <v>2.78</v>
       </c>
       <c r="I20" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>2.92</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
         <v>2.84</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
         <v>4.1</v>
@@ -4458,7 +4458,7 @@
         <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G22" t="n">
         <v>2.22</v>
@@ -4652,7 +4652,7 @@
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.27</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
         <v>1.76</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.97</v>
       </c>
       <c r="G24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H24" t="n">
         <v>3.95</v>
@@ -5076,7 +5076,7 @@
         <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X24" t="n">
         <v>14</v>
@@ -5127,10 +5127,10 @@
         <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP24" t="n">
         <v>12.5</v>
@@ -5139,13 +5139,13 @@
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5178,17 +5178,17 @@
         <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF24" t="n">
         <v>12</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
         <v>2.1</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
         <v>14.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD26" t="n">
         <v>17</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
         <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P27" t="n">
         <v>2.02</v>
@@ -5643,10 +5643,10 @@
         <v>1.82</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
         <v>1.66</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.9</v>
       </c>
       <c r="G28" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="H28" t="n">
         <v>4.3</v>
@@ -5849,10 +5849,10 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="X28" t="n">
         <v>15.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H30" t="n">
         <v>2.18</v>
@@ -6204,7 +6204,7 @@
         <v>2.92</v>
       </c>
       <c r="K30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,10 +6213,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O30" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P30" t="n">
         <v>1.54</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6407,10 +6407,10 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
         <v>1.69</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="G33" t="n">
         <v>3.8</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="I33" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="J33" t="n">
         <v>3.15</v>
@@ -6798,13 +6798,13 @@
         <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -6819,7 +6819,7 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W33" t="n">
         <v>1.36</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6989,16 +6989,16 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="O34" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7183,16 +7183,16 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P35" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R35" t="n">
         <v>1.19</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>2.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K36" t="n">
         <v>4.3</v>
@@ -7377,16 +7377,16 @@
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="O36" t="n">
         <v>1.21</v>
       </c>
       <c r="P36" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
@@ -7458,65 +7458,65 @@
         <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP36" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AV36" t="n">
         <v>2.3</v>
       </c>
-      <c r="AR36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS36" t="n">
+      <c r="AW36" t="n">
         <v>2.48</v>
       </c>
-      <c r="AT36" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AX36" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AY36" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD36" t="n">
         <v>2.62</v>
       </c>
-      <c r="BC36" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BE36" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BG36" t="n">
         <v>7.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="H37" t="n">
         <v>2.4</v>
       </c>
       <c r="I37" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
         <v>3.6</v>
@@ -7571,13 +7571,13 @@
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
         <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
         <v>1.64</v>
@@ -7586,7 +7586,7 @@
         <v>1.43</v>
       </c>
       <c r="S37" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T37" t="n">
         <v>1.55</v>
@@ -7595,7 +7595,7 @@
         <v>2.1</v>
       </c>
       <c r="V37" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W37" t="n">
         <v>1.48</v>
@@ -7613,7 +7613,7 @@
         <v>980</v>
       </c>
       <c r="AB37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC37" t="n">
         <v>10.5</v>
@@ -7658,59 +7658,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
       </c>
       <c r="AU37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>15.5</v>
+        <v>3.7</v>
       </c>
       <c r="AY37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD37" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG37" t="n">
         <v>13</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G38" t="n">
         <v>2.48</v>
@@ -7756,7 +7756,7 @@
         <v>2.84</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,10 +7765,10 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O38" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
@@ -7789,7 +7789,7 @@
         <v>1.75</v>
       </c>
       <c r="V38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
         <v>1.67</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>1.35</v>
@@ -7968,7 +7968,7 @@
         <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R39" t="n">
         <v>1.22</v>
@@ -7998,7 +7998,7 @@
         <v>25</v>
       </c>
       <c r="AA39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB39" t="n">
         <v>15</v>
@@ -8010,7 +8010,7 @@
         <v>17.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF39" t="n">
         <v>26</v>
@@ -8052,7 +8052,7 @@
         <v>12.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.74</v>
+        <v>27</v>
       </c>
       <c r="AT39" t="n">
         <v>2.34</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
         <v>1.66</v>
       </c>
       <c r="U40" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V40" t="n">
         <v>1.31</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G41" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H41" t="n">
         <v>3.85</v>
@@ -8338,7 +8338,7 @@
         <v>3.45</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8359,7 +8359,7 @@
         <v>1.96</v>
       </c>
       <c r="R41" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
         <v>3.45</v>
@@ -8374,19 +8374,19 @@
         <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X41" t="n">
         <v>17.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z41" t="n">
         <v>36</v>
       </c>
       <c r="AA41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB41" t="n">
         <v>11.5</v>
@@ -8407,7 +8407,7 @@
         <v>13</v>
       </c>
       <c r="AH41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
         <v>70</v>
@@ -8422,25 +8422,25 @@
         <v>980</v>
       </c>
       <c r="AM41" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN41" t="n">
         <v>19</v>
       </c>
       <c r="AO41" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ41" t="n">
         <v>12.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT41" t="n">
         <v>8.199999999999999</v>
@@ -8449,10 +8449,10 @@
         <v>7.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX41" t="n">
         <v>3.7</v>
@@ -8461,32 +8461,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB41" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BC41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD41" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>4</v>
-      </c>
       <c r="BE41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF41" t="n">
         <v>3.85</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
         <v>1.98</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.04</v>
+        <v>20</v>
       </c>
       <c r="AS42" t="n">
         <v>2.1</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>1.06</v>
       </c>
       <c r="G43" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="H43" t="n">
         <v>17.5</v>
@@ -8723,7 +8723,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -8738,16 +8738,16 @@
         <v>3.85</v>
       </c>
       <c r="O43" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="P43" t="n">
         <v>3.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S43" t="n">
         <v>1.47</v>
@@ -8762,7 +8762,7 @@
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G44" t="n">
         <v>1.99</v>
@@ -8935,13 +8935,13 @@
         <v>1.23</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q44" t="n">
         <v>1.68</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
         <v>2.72</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G45" t="n">
         <v>2.22</v>
@@ -9252,7 +9252,7 @@
         <v>10</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BF45" t="n">
         <v>16</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9511,13 +9511,13 @@
         <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="O47" t="n">
         <v>1.4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q47" t="n">
         <v>2.24</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>1.53</v>
       </c>
       <c r="G48" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="H48" t="n">
         <v>5.2</v>
@@ -9693,7 +9693,7 @@
         <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="K48" t="n">
         <v>6.6</v>
@@ -9714,7 +9714,7 @@
         <v>3.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="R48" t="n">
         <v>1.9</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G49" t="n">
         <v>2.66</v>
@@ -9908,7 +9908,7 @@
         <v>2.56</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R49" t="n">
         <v>1.63</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="G50" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H50" t="n">
         <v>6.4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G51" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H51" t="n">
         <v>2.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J51" t="n">
         <v>3.1</v>
       </c>
       <c r="K51" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10311,7 +10311,7 @@
         <v>1.83</v>
       </c>
       <c r="V51" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W51" t="n">
         <v>1.27</v>
@@ -10359,7 +10359,7 @@
         <v>80</v>
       </c>
       <c r="AL51" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AM51" t="n">
         <v>190</v>
@@ -10380,7 +10380,7 @@
         <v>10.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT51" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
         <v>9.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY51" t="n">
         <v>14.5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G52" t="n">
         <v>2.32</v>
@@ -10466,7 +10466,7 @@
         <v>3.35</v>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>3.55</v>
@@ -10481,13 +10481,13 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="O52" t="n">
         <v>1.24</v>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q52" t="n">
         <v>1.75</v>
@@ -10496,7 +10496,7 @@
         <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
         <v>2.52</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R53" t="n">
         <v>1.54</v>
@@ -10774,7 +10774,7 @@
         <v>2.46</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV53" t="n">
         <v>2.56</v>
@@ -10786,7 +10786,7 @@
         <v>2.48</v>
       </c>
       <c r="AY53" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="AZ53" t="n">
         <v>2.54</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
         <v>1.03</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -10881,13 +10881,13 @@
         <v>1.58</v>
       </c>
       <c r="R54" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S54" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T54" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U54" t="n">
         <v>2.36</v>
@@ -10959,7 +10959,7 @@
         <v>10.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS54" t="n">
         <v>18</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G55" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H55" t="n">
         <v>6.8</v>
@@ -11051,7 +11051,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K55" t="n">
         <v>3.85</v>
@@ -11063,10 +11063,10 @@
         <v>1.12</v>
       </c>
       <c r="N55" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P55" t="n">
         <v>1.54</v>
@@ -11081,16 +11081,16 @@
         <v>5.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="U55" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V55" t="n">
         <v>1.14</v>
       </c>
       <c r="W55" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X55" t="n">
         <v>10.5</v>
@@ -11147,7 +11147,7 @@
         <v>350</v>
       </c>
       <c r="AP55" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ55" t="n">
         <v>5.9</v>
@@ -11174,7 +11174,7 @@
         <v>7.2</v>
       </c>
       <c r="AY55" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ55" t="n">
         <v>6.8</v>
@@ -11183,7 +11183,7 @@
         <v>2.48</v>
       </c>
       <c r="BB55" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="BC55" t="n">
         <v>6.2</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11239,13 +11239,13 @@
         <v>3.9</v>
       </c>
       <c r="H56" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I56" t="n">
         <v>2.86</v>
       </c>
       <c r="J56" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K56" t="n">
         <v>3.1</v>
@@ -11257,7 +11257,7 @@
         <v>1.15</v>
       </c>
       <c r="N56" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O56" t="n">
         <v>1.66</v>
@@ -11275,13 +11275,13 @@
         <v>6.4</v>
       </c>
       <c r="T56" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U56" t="n">
         <v>1.63</v>
       </c>
       <c r="V56" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W56" t="n">
         <v>1.34</v>
@@ -11341,7 +11341,7 @@
         <v>60</v>
       </c>
       <c r="AP56" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ56" t="n">
         <v>6</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
         <v>11.5</v>
       </c>
       <c r="K57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L57" t="n">
         <v>1.16</v>
@@ -11451,7 +11451,7 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="O57" t="n">
         <v>1.07</v>
@@ -11463,7 +11463,7 @@
         <v>1.25</v>
       </c>
       <c r="R57" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S57" t="n">
         <v>1.65</v>
@@ -11487,7 +11487,7 @@
         <v>1000</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA57" t="n">
         <v>1000</v>
@@ -11499,10 +11499,10 @@
         <v>32</v>
       </c>
       <c r="AD57" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF57" t="n">
         <v>12</v>
@@ -11517,13 +11517,13 @@
         <v>1000</v>
       </c>
       <c r="AJ57" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK57" t="n">
         <v>12.5</v>
       </c>
       <c r="AL57" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM57" t="n">
         <v>1000</v>
@@ -11535,7 +11535,7 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AQ57" t="n">
         <v>36</v>
@@ -11544,16 +11544,16 @@
         <v>48</v>
       </c>
       <c r="AS57" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT57" t="n">
         <v>17.5</v>
       </c>
       <c r="AU57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV57" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AW57" t="n">
         <v>50</v>
@@ -11565,7 +11565,7 @@
         <v>13</v>
       </c>
       <c r="AZ57" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BA57" t="n">
         <v>42</v>
@@ -11583,14 +11583,14 @@
         <v>42</v>
       </c>
       <c r="BF57" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BG57" t="n">
         <v>48</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G58" t="n">
         <v>2.74</v>
@@ -11630,10 +11630,10 @@
         <v>2.68</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J58" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K58" t="n">
         <v>4.1</v>
@@ -11651,19 +11651,19 @@
         <v>1.23</v>
       </c>
       <c r="P58" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R58" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S58" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="T58" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="U58" t="n">
         <v>2.36</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11818,19 +11818,19 @@
         <v>2.48</v>
       </c>
       <c r="G59" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H59" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>3.65</v>
       </c>
       <c r="K59" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -11863,10 +11863,10 @@
         <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W59" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12206,19 +12206,19 @@
         <v>1.52</v>
       </c>
       <c r="G61" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H61" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K61" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,16 +12227,16 @@
         <v>1.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O61" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P61" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R61" t="n">
         <v>1.22</v>
@@ -12254,7 +12254,7 @@
         <v>1.11</v>
       </c>
       <c r="W61" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X61" t="n">
         <v>12</v>
@@ -12269,7 +12269,7 @@
         <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC61" t="n">
         <v>980</v>
@@ -12281,7 +12281,7 @@
         <v>220</v>
       </c>
       <c r="AF61" t="n">
-        <v>980</v>
+        <v>7.8</v>
       </c>
       <c r="AG61" t="n">
         <v>980</v>
@@ -12311,62 +12311,62 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AQ61" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR61" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS61" t="n">
-        <v>9.6</v>
+        <v>2.32</v>
       </c>
       <c r="AT61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU61" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV61" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW61" t="n">
-        <v>9.4</v>
+        <v>2.32</v>
       </c>
       <c r="AX61" t="n">
         <v>6.6</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AZ61" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA61" t="n">
-        <v>9.4</v>
+        <v>2.32</v>
       </c>
       <c r="BB61" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC61" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD61" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.3</v>
+        <v>2.32</v>
       </c>
       <c r="BF61" t="n">
         <v>10</v>
       </c>
       <c r="BG61" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12508,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR62" t="n">
         <v>55</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12615,10 +12615,10 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O63" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P63" t="n">
         <v>1.57</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12791,16 +12791,16 @@
         <v>5.4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I64" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="J64" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,13 +12809,13 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="O64" t="n">
         <v>1.27</v>
       </c>
       <c r="P64" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q64" t="n">
         <v>1.78</v>
@@ -12830,10 +12830,10 @@
         <v>1.73</v>
       </c>
       <c r="U64" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="W64" t="n">
         <v>1.22</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
         <v>3.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M65" t="n">
         <v>1.09</v>
@@ -13084,7 +13084,7 @@
         <v>32</v>
       </c>
       <c r="AO65" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP65" t="n">
         <v>9.800000000000001</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13197,10 +13197,10 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O66" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P66" t="n">
         <v>1.74</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
         <v>1.11</v>
       </c>
       <c r="P68" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q68" t="n">
         <v>1.35</v>
@@ -13600,7 +13600,7 @@
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T68" t="n">
         <v>1.62</v>
@@ -13660,7 +13660,7 @@
         <v>23</v>
       </c>
       <c r="AM68" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN68" t="n">
         <v>3.6</v>
@@ -13675,10 +13675,10 @@
         <v>40</v>
       </c>
       <c r="AR68" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS68" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT68" t="n">
         <v>14.5</v>
@@ -13690,7 +13690,7 @@
         <v>29</v>
       </c>
       <c r="AW68" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX68" t="n">
         <v>11</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
         <v>1.75</v>
       </c>
       <c r="O69" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P69" t="n">
         <v>1.75</v>
@@ -13791,10 +13791,10 @@
         <v>1.78</v>
       </c>
       <c r="R69" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="S69" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13982,13 +13982,13 @@
         <v>1.49</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R70" t="n">
         <v>1.13</v>
       </c>
       <c r="S70" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T70" t="n">
         <v>1.01</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14152,13 +14152,13 @@
         <v>3.15</v>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>3.3</v>
       </c>
       <c r="K71" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14191,7 +14191,7 @@
         <v>1.01</v>
       </c>
       <c r="V71" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W71" t="n">
         <v>1.61</v>
@@ -14206,7 +14206,7 @@
         <v>30</v>
       </c>
       <c r="AA71" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB71" t="n">
         <v>11</v>
@@ -14218,7 +14218,7 @@
         <v>20</v>
       </c>
       <c r="AE71" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF71" t="n">
         <v>20</v>
@@ -14230,7 +14230,7 @@
         <v>30</v>
       </c>
       <c r="AI71" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ71" t="n">
         <v>50</v>
@@ -14251,25 +14251,25 @@
         <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AQ71" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS71" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AV71" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AW71" t="n">
         <v>2.3</v>
@@ -14278,35 +14278,35 @@
         <v>10.5</v>
       </c>
       <c r="AY71" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AZ71" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BA71" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BB71" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BC71" t="n">
         <v>22</v>
       </c>
       <c r="BD71" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BE71" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BG71" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
         <v>3.8</v>
       </c>
       <c r="L72" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M72" t="n">
         <v>1.09</v>
@@ -14367,7 +14367,7 @@
         <v>1.45</v>
       </c>
       <c r="P72" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q72" t="n">
         <v>2.42</v>
@@ -14406,7 +14406,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC72" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD72" t="n">
         <v>21</v>
@@ -14418,7 +14418,7 @@
         <v>1000</v>
       </c>
       <c r="AG72" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH72" t="n">
         <v>1000</v>
@@ -14448,59 +14448,59 @@
         <v>9.4</v>
       </c>
       <c r="AQ72" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AR72" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS72" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AU72" t="n">
         <v>6.6</v>
       </c>
       <c r="AV72" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX72" t="n">
         <v>9.6</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ72" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA72" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB72" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>4.2</v>
       </c>
       <c r="BC72" t="n">
         <v>21</v>
       </c>
       <c r="BD72" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE72" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF72" t="n">
         <v>16</v>
       </c>
       <c r="BG72" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14555,7 @@
         <v>1.06</v>
       </c>
       <c r="N73" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O73" t="n">
         <v>1.28</v>
@@ -14567,7 +14567,7 @@
         <v>1.87</v>
       </c>
       <c r="R73" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S73" t="n">
         <v>3.1</v>
@@ -14684,7 +14684,7 @@
         <v>40</v>
       </c>
       <c r="BE73" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF73" t="n">
         <v>30</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G74" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="H74" t="n">
         <v>4.7</v>
@@ -14755,7 +14755,7 @@
         <v>1.33</v>
       </c>
       <c r="P74" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q74" t="n">
         <v>1.99</v>
@@ -14767,16 +14767,16 @@
         <v>3.55</v>
       </c>
       <c r="T74" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="U74" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="V74" t="n">
         <v>1.23</v>
       </c>
       <c r="W74" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X74" t="n">
         <v>16</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15113,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G76" t="n">
         <v>1.57</v>
       </c>
       <c r="H76" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I76" t="n">
         <v>1000</v>
       </c>
       <c r="J76" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K76" t="n">
-        <v>6.2</v>
+        <v>85</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15161,7 +15161,7 @@
         <v>1.01</v>
       </c>
       <c r="V76" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W76" t="n">
         <v>2.74</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
         <v>7.6</v>
       </c>
       <c r="J78" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="K78" t="n">
         <v>4.1</v>
@@ -15528,7 +15528,7 @@
         <v>2.6</v>
       </c>
       <c r="O78" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P78" t="n">
         <v>1.56</v>
@@ -15546,10 +15546,10 @@
         <v>2.2</v>
       </c>
       <c r="U78" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V78" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W78" t="n">
         <v>2.06</v>
@@ -15561,7 +15561,7 @@
         <v>970</v>
       </c>
       <c r="Z78" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA78" t="n">
         <v>1000</v>
@@ -15609,62 +15609,62 @@
         <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ78" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU78" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS78" t="n">
+      <c r="AV78" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW78" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT78" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AX78" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AY78" t="n">
         <v>4</v>
       </c>
       <c r="AZ78" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC78" t="n">
         <v>3.55</v>
       </c>
-      <c r="BA78" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BD78" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE78" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF78" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG78" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15773,7 +15773,7 @@
         <v>1000</v>
       </c>
       <c r="AF79" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG79" t="n">
         <v>11</v>
@@ -15806,13 +15806,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ79" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR79" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS79" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT79" t="n">
         <v>5.8</v>
@@ -15821,10 +15821,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV79" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW79" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX79" t="n">
         <v>6.2</v>
@@ -15833,10 +15833,10 @@
         <v>9</v>
       </c>
       <c r="AZ79" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA79" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB79" t="n">
         <v>9.6</v>
@@ -15848,17 +15848,17 @@
         <v>40</v>
       </c>
       <c r="BE79" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF79" t="n">
         <v>6.2</v>
       </c>
       <c r="BG79" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16086,10 +16086,10 @@
         <v>2.74</v>
       </c>
       <c r="G81" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H81" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I81" t="n">
         <v>3.05</v>
@@ -16098,7 +16098,7 @@
         <v>3.3</v>
       </c>
       <c r="K81" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16134,7 +16134,7 @@
         <v>1.49</v>
       </c>
       <c r="W81" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
         <v>1.87</v>
       </c>
       <c r="G82" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H82" t="n">
         <v>4.6</v>
@@ -16292,7 +16292,7 @@
         <v>3.3</v>
       </c>
       <c r="K82" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16328,7 +16328,7 @@
         <v>1.19</v>
       </c>
       <c r="W82" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G83" t="n">
         <v>3.3</v>
@@ -16480,13 +16480,13 @@
         <v>2.38</v>
       </c>
       <c r="I83" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J83" t="n">
         <v>3.45</v>
       </c>
       <c r="K83" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L83" t="n">
         <v>1.01</v>
@@ -16495,16 +16495,16 @@
         <v>1.05</v>
       </c>
       <c r="N83" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
         <v>1.26</v>
       </c>
       <c r="P83" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R83" t="n">
         <v>1.32</v>
@@ -16519,7 +16519,7 @@
         <v>1.83</v>
       </c>
       <c r="V83" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W83" t="n">
         <v>1.43</v>
@@ -16540,7 +16540,7 @@
         <v>19</v>
       </c>
       <c r="AC83" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD83" t="n">
         <v>17</v>
@@ -16558,7 +16558,7 @@
         <v>24</v>
       </c>
       <c r="AI83" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ83" t="n">
         <v>70</v>
@@ -16579,62 +16579,62 @@
         <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AT83" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AU83" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AV83" t="n">
         <v>9.4</v>
       </c>
       <c r="AW83" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX83" t="n">
         <v>2.06</v>
       </c>
-      <c r="AX83" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AY83" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BA83" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BB83" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BC83" t="n">
         <v>2.1</v>
       </c>
-      <c r="BC83" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BD83" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BE83" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BF83" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BG83" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
         <v>4.4</v>
       </c>
       <c r="T84" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="U84" t="n">
         <v>1.92</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
         <v>1.88</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.26</v>
@@ -787,28 +787,28 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -817,7 +817,7 @@
         <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>100</v>
@@ -829,7 +829,7 @@
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -844,13 +844,13 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL2" t="n">
         <v>26</v>
@@ -859,10 +859,10 @@
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -874,10 +874,10 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>9.6</v>
@@ -886,22 +886,22 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -910,17 +910,17 @@
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
         <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
         <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
         <v>2.34</v>
@@ -1011,10 +1011,10 @@
         <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>4.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS3" t="n">
         <v>3.45</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
         <v>3.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>1.37</v>
       </c>
       <c r="H4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
@@ -1163,34 +1163,34 @@
         <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
         <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
         <v>1.09</v>
@@ -1208,7 +1208,7 @@
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
@@ -1235,7 +1235,7 @@
         <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1250,28 +1250,28 @@
         <v>5.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="n">
         <v>12.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
@@ -1298,7 +1298,7 @@
         <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>4.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1339,70 +1339,70 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X5" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
         <v>980</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1414,7 +1414,7 @@
         <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
@@ -1423,37 +1423,37 @@
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>980</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
         <v>4.3</v>
@@ -1462,10 +1462,10 @@
         <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1474,10 +1474,10 @@
         <v>3.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,7 +1486,7 @@
         <v>3.45</v>
       </c>
       <c r="BC5" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BD5" t="n">
         <v>3.95</v>
@@ -1495,14 +1495,14 @@
         <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1966,13 +1966,13 @@
         <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
         <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X8" t="n">
         <v>15.5</v>
@@ -2056,13 +2056,13 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
         <v>19.5</v>
@@ -2071,20 +2071,20 @@
         <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
         <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
         <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="G9" t="n">
         <v>1.7</v>
@@ -2130,10 +2130,10 @@
         <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
@@ -2148,13 +2148,13 @@
         <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
         <v>1.09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,7 +2163,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
         <v>2.44</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
         <v>2.28</v>
@@ -2318,7 +2318,7 @@
         <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2327,28 +2327,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>1.03</v>
       </c>
       <c r="O10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN11" t="n">
         <v>10</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G12" t="n">
         <v>1.86</v>
@@ -2712,43 +2712,43 @@
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.36</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.08</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
         <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2760,7 +2760,7 @@
         <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
         <v>9</v>
@@ -2805,7 +2805,7 @@
         <v>150</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>3.9</v>
@@ -2823,7 +2823,7 @@
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW12" t="n">
         <v>4.2</v>
@@ -2856,11 +2856,11 @@
         <v>3.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I13" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
         <v>3.9</v>
@@ -2921,13 +2921,13 @@
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>3.35</v>
@@ -2939,10 +2939,10 @@
         <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
         <v>980</v>
@@ -2981,7 +2981,7 @@
         <v>980</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
         <v>980</v>
@@ -2999,62 +2999,62 @@
         <v>980</v>
       </c>
       <c r="AP13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3127,10 +3127,10 @@
         <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.1</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
@@ -3303,25 +3303,25 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.81</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
         <v>1.94</v>
@@ -3330,7 +3330,7 @@
         <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>2.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
         <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3500,13 +3500,13 @@
         <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
         <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
         <v>1.79</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3894,13 +3894,13 @@
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.43</v>
+        <v>2.74</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4088,19 +4088,19 @@
         <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
         <v>3.65</v>
@@ -4273,22 +4273,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
         <v>1.02</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
         <v>3.25</v>
@@ -4455,10 +4455,10 @@
         <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O21" t="n">
         <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
         <v>1.94</v>
@@ -4494,7 +4494,7 @@
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4688,7 +4688,7 @@
         <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>1.76</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.8</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
         <v>3.55</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
         <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X24" t="n">
         <v>14</v>
@@ -5091,13 +5091,13 @@
         <v>110</v>
       </c>
       <c r="AB24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>55</v>
@@ -5112,13 +5112,13 @@
         <v>980</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
         <v>980</v>
@@ -5127,25 +5127,25 @@
         <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5154,7 +5154,7 @@
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX24" t="n">
         <v>11</v>
@@ -5178,17 +5178,17 @@
         <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>2.96</v>
       </c>
       <c r="G25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H25" t="n">
         <v>2.08</v>
@@ -5264,7 +5264,7 @@
         <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V25" t="n">
         <v>1.65</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -5428,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.26</v>
@@ -5446,16 +5446,16 @@
         <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U26" t="n">
         <v>2.6</v>
@@ -5464,7 +5464,7 @@
         <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X26" t="n">
         <v>29</v>
@@ -5557,7 +5557,7 @@
         <v>9</v>
       </c>
       <c r="BB26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
         <v>16</v>
@@ -5569,14 +5569,14 @@
         <v>36</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG26" t="n">
         <v>20</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5628,10 +5628,10 @@
         <v>1.28</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
         <v>1.24</v>
@@ -5643,16 +5643,16 @@
         <v>1.82</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U27" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V27" t="n">
         <v>1.36</v>
@@ -5715,7 +5715,7 @@
         <v>40</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
         <v>12.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G28" t="n">
         <v>1.95</v>
@@ -5810,13 +5810,13 @@
         <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>1.32</v>
@@ -5828,16 +5828,16 @@
         <v>3.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
         <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
         <v>3.65</v>
@@ -5849,7 +5849,7 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
         <v>2.04</v>
@@ -5864,7 +5864,7 @@
         <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB28" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
         <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="n">
         <v>23</v>
@@ -5915,7 +5915,7 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS28" t="n">
         <v>6.4</v>
@@ -5951,7 +5951,7 @@
         <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE28" t="n">
         <v>6.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G29" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H29" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="I29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>3.5</v>
@@ -6025,7 +6025,7 @@
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
         <v>1.7</v>
@@ -6037,17 +6037,17 @@
         <v>2.62</v>
       </c>
       <c r="T29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.53</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X29" t="n">
         <v>1000</v>
       </c>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6192,167 +6192,167 @@
         <v>3.65</v>
       </c>
       <c r="G30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS30" t="n">
         <v>4.6</v>
       </c>
-      <c r="H30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="G31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J31" t="n">
         <v>3.1</v>
@@ -6407,16 +6407,16 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
         <v>1.2</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G32" t="n">
         <v>4.7</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I32" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
         <v>3.55</v>
@@ -6598,19 +6598,19 @@
         <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
         <v>1.62</v>
       </c>
       <c r="O32" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P32" t="n">
         <v>1.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
@@ -6619,13 +6619,13 @@
         <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
         <v>1.27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="G33" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H33" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -6795,16 +6795,16 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.93</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
         <v>4.1</v>
@@ -6977,7 +6977,7 @@
         <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
         <v>3.8</v>
@@ -6989,13 +6989,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
         <v>1.96</v>
@@ -7016,7 +7016,7 @@
         <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7165,16 +7165,16 @@
         <v>6.2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I35" t="n">
         <v>2.02</v>
       </c>
       <c r="J35" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L35" t="n">
         <v>1.39</v>
@@ -7183,22 +7183,22 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="O35" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R35" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>2</v>
@@ -7207,16 +7207,16 @@
         <v>1.8</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
         <v>12.5</v>
@@ -7225,10 +7225,10 @@
         <v>26</v>
       </c>
       <c r="AB35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD35" t="n">
         <v>12.5</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="AF35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG35" t="n">
         <v>24</v>
@@ -7249,10 +7249,10 @@
         <v>55</v>
       </c>
       <c r="AJ35" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK35" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL35" t="n">
         <v>110</v>
@@ -7261,7 +7261,7 @@
         <v>190</v>
       </c>
       <c r="AN35" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO35" t="n">
         <v>21</v>
@@ -7273,13 +7273,13 @@
         <v>6.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS35" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU35" t="n">
         <v>6.8</v>
@@ -7288,41 +7288,41 @@
         <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY35" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG35" t="n">
         <v>14</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H36" t="n">
         <v>1.96</v>
@@ -7365,10 +7365,10 @@
         <v>2.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,13 +7377,13 @@
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="O36" t="n">
         <v>1.21</v>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
         <v>1.69</v>
@@ -7392,7 +7392,7 @@
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7404,7 +7404,7 @@
         <v>1.9</v>
       </c>
       <c r="W36" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X36" t="n">
         <v>28</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7550,10 +7550,10 @@
         <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I37" t="n">
         <v>2.7</v>
@@ -7562,7 +7562,7 @@
         <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7628,7 +7628,7 @@
         <v>980</v>
       </c>
       <c r="AG37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH37" t="n">
         <v>19.5</v>
@@ -7661,10 +7661,10 @@
         <v>3.35</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
@@ -7673,13 +7673,13 @@
         <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY37" t="n">
         <v>9.800000000000001</v>
@@ -7688,16 +7688,16 @@
         <v>3.55</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB37" t="n">
         <v>4</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE37" t="n">
         <v>4.1</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.12</v>
       </c>
       <c r="G38" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="H38" t="n">
         <v>3.95</v>
@@ -7753,7 +7753,7 @@
         <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K38" t="n">
         <v>3.65</v>
@@ -7765,13 +7765,13 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
         <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q38" t="n">
         <v>2.2</v>
@@ -7789,10 +7789,10 @@
         <v>1.75</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7935,170 +7935,170 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G39" t="n">
         <v>3.15</v>
       </c>
       <c r="H39" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J39" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
         <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U39" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AB39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR39" t="n">
         <v>15</v>
       </c>
-      <c r="AC39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AS39" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.34</v>
+        <v>9</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.72</v>
+        <v>6.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="AY39" t="n">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="BB39" t="n">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.64</v>
+        <v>6.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
         <v>3.8</v>
       </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>3.7</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8168,16 +8168,16 @@
         <v>1.45</v>
       </c>
       <c r="S40" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T40" t="n">
         <v>1.66</v>
       </c>
       <c r="U40" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V40" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W40" t="n">
         <v>1.92</v>
@@ -8186,16 +8186,16 @@
         <v>20</v>
       </c>
       <c r="Y40" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z40" t="n">
         <v>34</v>
       </c>
       <c r="AA40" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC40" t="n">
         <v>9.6</v>
@@ -8204,19 +8204,19 @@
         <v>17.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AF40" t="n">
         <v>14.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH40" t="n">
         <v>18</v>
       </c>
       <c r="AI40" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AJ40" t="n">
         <v>24</v>
@@ -8246,7 +8246,7 @@
         <v>25</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT40" t="n">
         <v>9.4</v>
@@ -8258,7 +8258,7 @@
         <v>14</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX40" t="n">
         <v>11.5</v>
@@ -8270,7 +8270,7 @@
         <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB40" t="n">
         <v>19</v>
@@ -8279,20 +8279,20 @@
         <v>16.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF40" t="n">
         <v>8.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
         <v>4.3</v>
       </c>
       <c r="J41" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K41" t="n">
         <v>4</v>
@@ -8347,13 +8347,13 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q41" t="n">
         <v>1.96</v>
@@ -8374,7 +8374,7 @@
         <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X41" t="n">
         <v>17.5</v>
@@ -8398,7 +8398,7 @@
         <v>20</v>
       </c>
       <c r="AE41" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF41" t="n">
         <v>16</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H42" t="n">
         <v>3.25</v>
       </c>
       <c r="I42" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J42" t="n">
         <v>3.7</v>
       </c>
       <c r="K42" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,10 +8541,10 @@
         <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P42" t="n">
         <v>2.24</v>
@@ -8553,10 +8553,10 @@
         <v>1.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="T42" t="n">
         <v>1.6</v>
@@ -8565,122 +8565,122 @@
         <v>2.36</v>
       </c>
       <c r="V42" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y42" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Z42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE42" t="n">
         <v>38</v>
       </c>
-      <c r="AA42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>50</v>
-      </c>
       <c r="AF42" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ42" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AK42" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AL42" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.14</v>
+        <v>18</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.98</v>
+        <v>14</v>
       </c>
       <c r="AR42" t="n">
         <v>20</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.95</v>
+        <v>12.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.97</v>
+        <v>13.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.97</v>
+        <v>13</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>2.04</v>
+        <v>22</v>
       </c>
       <c r="BC42" t="n">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.04</v>
+        <v>23</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.1</v>
+        <v>50</v>
       </c>
       <c r="BF42" t="n">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.14</v>
+        <v>21</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G43" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="H43" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -8735,146 +8735,146 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P43" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>330</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>55</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>430</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN43" t="n">
         <v>2.2</v>
       </c>
-      <c r="S43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO43" t="n">
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,34 +8929,34 @@
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.23</v>
       </c>
       <c r="P44" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R44" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S44" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T44" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="U44" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V44" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X44" t="n">
         <v>24</v>
@@ -8971,7 +8971,7 @@
         <v>110</v>
       </c>
       <c r="AB44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC44" t="n">
         <v>11.5</v>
@@ -8983,10 +8983,10 @@
         <v>980</v>
       </c>
       <c r="AF44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH44" t="n">
         <v>21</v>
@@ -8995,10 +8995,10 @@
         <v>55</v>
       </c>
       <c r="AJ44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL44" t="n">
         <v>980</v>
@@ -9013,7 +9013,7 @@
         <v>980</v>
       </c>
       <c r="AP44" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ44" t="n">
         <v>15.5</v>
@@ -9022,7 +9022,7 @@
         <v>4.9</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT44" t="n">
         <v>9.4</v>
@@ -9034,7 +9034,7 @@
         <v>14.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX44" t="n">
         <v>11</v>
@@ -9046,10 +9046,10 @@
         <v>14.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC44" t="n">
         <v>15.5</v>
@@ -9058,17 +9058,17 @@
         <v>4.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF44" t="n">
         <v>7.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G45" t="n">
         <v>2.22</v>
@@ -9114,7 +9114,7 @@
         <v>3.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -9123,16 +9123,16 @@
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P45" t="n">
         <v>1.71</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
         <v>1.26</v>
@@ -9141,7 +9141,7 @@
         <v>4.2</v>
       </c>
       <c r="T45" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U45" t="n">
         <v>1.92</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9305,10 +9305,10 @@
         <v>2.1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L46" t="n">
         <v>1.34</v>
@@ -9317,13 +9317,13 @@
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.27</v>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
         <v>1.81</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J47" t="n">
         <v>3.3</v>
       </c>
-      <c r="H47" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.72</v>
-      </c>
       <c r="K47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,13 +9511,13 @@
         <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="O47" t="n">
         <v>1.4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q47" t="n">
         <v>2.24</v>
@@ -9532,13 +9532,13 @@
         <v>1.89</v>
       </c>
       <c r="U47" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V47" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W47" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X47" t="n">
         <v>12.5</v>
@@ -9625,7 +9625,7 @@
         <v>4.2</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA47" t="n">
         <v>4.8</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9684,19 +9684,19 @@
         <v>1.53</v>
       </c>
       <c r="G48" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="H48" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K48" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,22 +9705,22 @@
         <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>1.08</v>
       </c>
       <c r="P48" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R48" t="n">
         <v>1.9</v>
       </c>
       <c r="S48" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W48" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9875,16 +9875,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G49" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H49" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="I49" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J49" t="n">
         <v>3.9</v>
@@ -9902,13 +9902,13 @@
         <v>5.6</v>
       </c>
       <c r="O49" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P49" t="n">
         <v>2.56</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R49" t="n">
         <v>1.63</v>
@@ -9923,10 +9923,10 @@
         <v>2.58</v>
       </c>
       <c r="V49" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X49" t="n">
         <v>32</v>
@@ -9935,13 +9935,13 @@
         <v>22</v>
       </c>
       <c r="Z49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB49" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC49" t="n">
         <v>12.5</v>
@@ -9950,10 +9950,10 @@
         <v>16.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG49" t="n">
         <v>15</v>
@@ -9965,34 +9965,34 @@
         <v>38</v>
       </c>
       <c r="AJ49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK49" t="n">
         <v>28</v>
       </c>
       <c r="AL49" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM49" t="n">
         <v>65</v>
       </c>
       <c r="AN49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ49" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR49" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT49" t="n">
         <v>14</v>
@@ -10001,22 +10001,22 @@
         <v>8.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX49" t="n">
         <v>17</v>
       </c>
       <c r="AY49" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ49" t="n">
         <v>12.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB49" t="n">
         <v>3.85</v>
@@ -10025,20 +10025,20 @@
         <v>19.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE49" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF49" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>1.43</v>
       </c>
       <c r="G50" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="H50" t="n">
         <v>6.4</v>
@@ -10105,10 +10105,10 @@
         <v>1.46</v>
       </c>
       <c r="R50" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S50" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -10120,7 +10120,7 @@
         <v>1.12</v>
       </c>
       <c r="W50" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10263,19 +10263,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G51" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="I51" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="J51" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K51" t="n">
         <v>3.45</v>
@@ -10287,16 +10287,16 @@
         <v>1.11</v>
       </c>
       <c r="N51" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="O51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
@@ -10305,25 +10305,25 @@
         <v>4.5</v>
       </c>
       <c r="T51" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V51" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="W51" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X51" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y51" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z51" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA51" t="n">
         <v>980</v>
@@ -10338,7 +10338,7 @@
         <v>13</v>
       </c>
       <c r="AE51" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF51" t="n">
         <v>980</v>
@@ -10359,28 +10359,28 @@
         <v>80</v>
       </c>
       <c r="AL51" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AM51" t="n">
         <v>190</v>
       </c>
       <c r="AN51" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AO51" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ51" t="n">
         <v>6.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT51" t="n">
         <v>10</v>
@@ -10392,41 +10392,41 @@
         <v>9.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY51" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG51" t="n">
         <v>19</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H52" t="n">
         <v>3.35</v>
@@ -10472,7 +10472,7 @@
         <v>3.55</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10487,7 +10487,7 @@
         <v>1.24</v>
       </c>
       <c r="P52" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
         <v>1.75</v>
@@ -10496,7 +10496,7 @@
         <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10508,7 +10508,7 @@
         <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G53" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H53" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I53" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>4.1</v>
@@ -10675,25 +10675,25 @@
         <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O53" t="n">
         <v>1.15</v>
       </c>
       <c r="P53" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R53" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S53" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U53" t="n">
         <v>1.01</v>
@@ -10702,7 +10702,7 @@
         <v>1.21</v>
       </c>
       <c r="W53" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X53" t="n">
         <v>34</v>
@@ -10729,13 +10729,13 @@
         <v>1000</v>
       </c>
       <c r="AF53" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG53" t="n">
         <v>15</v>
       </c>
       <c r="AH53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI53" t="n">
         <v>1000</v>
@@ -10744,7 +10744,7 @@
         <v>28</v>
       </c>
       <c r="AK53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL53" t="n">
         <v>36</v>
@@ -10774,7 +10774,7 @@
         <v>2.46</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="AV53" t="n">
         <v>2.56</v>
@@ -10792,7 +10792,7 @@
         <v>2.54</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BB53" t="n">
         <v>2.58</v>
@@ -10807,14 +10807,14 @@
         <v>2.76</v>
       </c>
       <c r="BF53" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG53" t="n">
         <v>2.84</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10857,10 +10857,10 @@
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10869,7 +10869,7 @@
         <v>1.03</v>
       </c>
       <c r="N54" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -10878,16 +10878,16 @@
         <v>2.36</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R54" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S54" t="n">
         <v>2.46</v>
       </c>
       <c r="T54" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U54" t="n">
         <v>2.36</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="W54" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X54" t="n">
         <v>980</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G55" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="H55" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I55" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J55" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K55" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,16 +11063,16 @@
         <v>1.12</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O55" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P55" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R55" t="n">
         <v>1.19</v>
@@ -11081,31 +11081,31 @@
         <v>5.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="U55" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V55" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W55" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="X55" t="n">
         <v>10.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z55" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA55" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB55" t="n">
-        <v>5.8</v>
+        <v>980</v>
       </c>
       <c r="AC55" t="n">
         <v>980</v>
@@ -11144,22 +11144,22 @@
         <v>21</v>
       </c>
       <c r="AO55" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR55" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS55" t="n">
         <v>2.48</v>
       </c>
       <c r="AT55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU55" t="n">
         <v>7.6</v>
@@ -11168,19 +11168,19 @@
         <v>6.8</v>
       </c>
       <c r="AW55" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX55" t="n">
         <v>7.2</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ55" t="n">
         <v>6.8</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.48</v>
+        <v>8</v>
       </c>
       <c r="BB55" t="n">
         <v>5.7</v>
@@ -11195,14 +11195,14 @@
         <v>2.48</v>
       </c>
       <c r="BF55" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG55" t="n">
         <v>2.48</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11239,13 +11239,13 @@
         <v>3.9</v>
       </c>
       <c r="H56" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I56" t="n">
         <v>2.86</v>
       </c>
       <c r="J56" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K56" t="n">
         <v>3.1</v>
@@ -11257,7 +11257,7 @@
         <v>1.15</v>
       </c>
       <c r="N56" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="O56" t="n">
         <v>1.66</v>
@@ -11281,7 +11281,7 @@
         <v>1.63</v>
       </c>
       <c r="V56" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W56" t="n">
         <v>1.34</v>
@@ -11341,19 +11341,19 @@
         <v>60</v>
       </c>
       <c r="AP56" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ56" t="n">
         <v>6</v>
       </c>
       <c r="AR56" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS56" t="n">
         <v>7.4</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU56" t="n">
         <v>6</v>
@@ -11365,7 +11365,7 @@
         <v>7.4</v>
       </c>
       <c r="AX56" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY56" t="n">
         <v>14.5</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
         <v>11.5</v>
       </c>
       <c r="K57" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="L57" t="n">
         <v>1.16</v>
@@ -11454,7 +11454,7 @@
         <v>12</v>
       </c>
       <c r="O57" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P57" t="n">
         <v>4.7</v>
@@ -11466,7 +11466,7 @@
         <v>2.44</v>
       </c>
       <c r="S57" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T57" t="n">
         <v>1.86</v>
@@ -11550,7 +11550,7 @@
         <v>17.5</v>
       </c>
       <c r="AU57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV57" t="n">
         <v>55</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         <v>2.56</v>
       </c>
       <c r="G58" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H58" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I58" t="n">
         <v>2.96</v>
@@ -11636,7 +11636,7 @@
         <v>3.6</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,22 +11645,22 @@
         <v>1.04</v>
       </c>
       <c r="N58" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O58" t="n">
         <v>1.23</v>
       </c>
       <c r="P58" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R58" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S58" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T58" t="n">
         <v>1.6</v>
@@ -11672,7 +11672,7 @@
         <v>1.52</v>
       </c>
       <c r="W58" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X58" t="n">
         <v>22</v>
@@ -11729,7 +11729,7 @@
         <v>24</v>
       </c>
       <c r="AP58" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ58" t="n">
         <v>12</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11815,46 +11815,46 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="G59" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="H59" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>3.65</v>
       </c>
       <c r="K59" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N59" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
         <v>1.23</v>
       </c>
       <c r="P59" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q59" t="n">
         <v>1.7</v>
       </c>
       <c r="R59" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S59" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="T59" t="n">
         <v>1.01</v>
@@ -11863,122 +11863,122 @@
         <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W59" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y59" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z59" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA59" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB59" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC59" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD59" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE59" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF59" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG59" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH59" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI59" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK59" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL59" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM59" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN59" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO59" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12009,13 +12009,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G60" t="n">
         <v>2.46</v>
       </c>
       <c r="H60" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I60" t="n">
         <v>3.75</v>
@@ -12024,7 +12024,7 @@
         <v>3.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L60" t="n">
         <v>1.47</v>
@@ -12033,7 +12033,7 @@
         <v>1.09</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O60" t="n">
         <v>1.41</v>
@@ -12042,7 +12042,7 @@
         <v>1.71</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R60" t="n">
         <v>1.26</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
         <v>1.62</v>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I61" t="n">
         <v>9.800000000000001</v>
@@ -12218,7 +12218,7 @@
         <v>3.85</v>
       </c>
       <c r="K61" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,16 +12227,16 @@
         <v>1.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="O61" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P61" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="R61" t="n">
         <v>1.22</v>
@@ -12263,7 +12263,7 @@
         <v>980</v>
       </c>
       <c r="Z61" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="n">
         <v>1000</v>
@@ -12311,10 +12311,10 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ61" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR61" t="n">
         <v>4.9</v>
@@ -12329,28 +12329,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV61" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW61" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="AX61" t="n">
         <v>6.6</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ61" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="BB61" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC61" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD61" t="n">
         <v>4.8</v>
@@ -12359,14 +12359,14 @@
         <v>2.32</v>
       </c>
       <c r="BF61" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BG61" t="n">
         <v>2.32</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12415,16 +12415,16 @@
         <v>4.3</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M62" t="n">
         <v>1.09</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P62" t="n">
         <v>1.83</v>
@@ -12433,10 +12433,10 @@
         <v>2.16</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T62" t="n">
         <v>2.26</v>
@@ -12445,10 +12445,10 @@
         <v>1.74</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X62" t="n">
         <v>12.5</v>
@@ -12463,10 +12463,10 @@
         <v>300</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD62" t="n">
         <v>29</v>
@@ -12505,13 +12505,13 @@
         <v>200</v>
       </c>
       <c r="AP62" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ62" t="n">
         <v>19</v>
       </c>
       <c r="AR62" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AS62" t="n">
         <v>50</v>
@@ -12541,7 +12541,7 @@
         <v>44</v>
       </c>
       <c r="BB62" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC62" t="n">
         <v>17</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12594,10 +12594,10 @@
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H63" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I63" t="n">
         <v>4.5</v>
@@ -12606,7 +12606,7 @@
         <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12615,10 +12615,10 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O63" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P63" t="n">
         <v>1.57</v>
@@ -12633,16 +12633,16 @@
         <v>3.5</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V63" t="n">
         <v>1.28</v>
       </c>
       <c r="W63" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12791,16 +12791,16 @@
         <v>5.4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="I64" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J64" t="n">
         <v>3.65</v>
       </c>
       <c r="K64" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,13 +12809,13 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
       <c r="O64" t="n">
         <v>1.27</v>
       </c>
       <c r="P64" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q64" t="n">
         <v>1.78</v>
@@ -12824,7 +12824,7 @@
         <v>1.21</v>
       </c>
       <c r="S64" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="T64" t="n">
         <v>1.73</v>
@@ -12833,10 +12833,10 @@
         <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="W64" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12979,25 +12979,25 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G65" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="H65" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
         <v>3.4</v>
       </c>
       <c r="J65" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K65" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M65" t="n">
         <v>1.09</v>
@@ -13006,37 +13006,37 @@
         <v>3.1</v>
       </c>
       <c r="O65" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P65" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R65" t="n">
         <v>1.26</v>
       </c>
       <c r="S65" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T65" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U65" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V65" t="n">
         <v>1.42</v>
       </c>
       <c r="W65" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X65" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z65" t="n">
         <v>23</v>
@@ -13045,61 +13045,61 @@
         <v>65</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC65" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD65" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE65" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF65" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG65" t="n">
         <v>12.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI65" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ65" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK65" t="n">
         <v>38</v>
       </c>
-      <c r="AK65" t="n">
-        <v>32</v>
-      </c>
       <c r="AL65" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM65" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN65" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO65" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP65" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ65" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR65" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS65" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT65" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU65" t="n">
         <v>6.6</v>
@@ -13108,41 +13108,41 @@
         <v>12</v>
       </c>
       <c r="AW65" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX65" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY65" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ65" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA65" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB65" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC65" t="n">
         <v>22</v>
       </c>
       <c r="BD65" t="n">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BE65" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF65" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BG65" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G66" t="n">
         <v>2.42</v>
@@ -13197,10 +13197,10 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O66" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P66" t="n">
         <v>1.74</v>
@@ -13218,7 +13218,7 @@
         <v>1.01</v>
       </c>
       <c r="U66" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V66" t="n">
         <v>1.25</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13564,13 +13564,13 @@
         <v>1.37</v>
       </c>
       <c r="G68" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H68" t="n">
         <v>8.4</v>
       </c>
       <c r="I68" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J68" t="n">
         <v>6.2</v>
@@ -13585,7 +13585,7 @@
         <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
         <v>1.11</v>
@@ -13594,25 +13594,25 @@
         <v>3.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R68" t="n">
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="T68" t="n">
         <v>1.62</v>
       </c>
       <c r="U68" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V68" t="n">
         <v>1.12</v>
       </c>
       <c r="W68" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X68" t="n">
         <v>48</v>
@@ -13630,7 +13630,7 @@
         <v>16.5</v>
       </c>
       <c r="AC68" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD68" t="n">
         <v>34</v>
@@ -13648,7 +13648,7 @@
         <v>22</v>
       </c>
       <c r="AI68" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ68" t="n">
         <v>14</v>
@@ -13660,25 +13660,25 @@
         <v>23</v>
       </c>
       <c r="AM68" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN68" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AO68" t="n">
         <v>70</v>
       </c>
       <c r="AP68" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AQ68" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR68" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AS68" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="AT68" t="n">
         <v>14.5</v>
@@ -13690,7 +13690,7 @@
         <v>29</v>
       </c>
       <c r="AW68" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AX68" t="n">
         <v>11</v>
@@ -13702,7 +13702,7 @@
         <v>19</v>
       </c>
       <c r="BA68" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BB68" t="n">
         <v>12</v>
@@ -13714,7 +13714,7 @@
         <v>20</v>
       </c>
       <c r="BE68" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="BF68" t="n">
         <v>3.45</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13755,170 +13755,170 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="G69" t="n">
         <v>3.45</v>
       </c>
       <c r="H69" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="I69" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="J69" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K69" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
       </c>
       <c r="M69" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P69" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="R69" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S69" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="T69" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U69" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V69" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W69" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X69" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y69" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB69" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC69" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD69" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE69" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF69" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG69" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH69" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI69" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK69" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL69" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM69" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN69" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO69" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV69" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX69" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY69" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ69" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA69" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC69" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD69" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE69" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF69" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG69" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
         <v>5.3</v>
       </c>
       <c r="H70" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I70" t="n">
         <v>2.58</v>
@@ -13964,7 +13964,7 @@
         <v>2.74</v>
       </c>
       <c r="K70" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -13982,13 +13982,13 @@
         <v>1.49</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R70" t="n">
         <v>1.13</v>
       </c>
       <c r="S70" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T70" t="n">
         <v>1.01</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G71" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H71" t="n">
         <v>3.15</v>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J71" t="n">
         <v>3.3</v>
       </c>
       <c r="K71" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14167,146 +14167,146 @@
         <v>1.11</v>
       </c>
       <c r="N71" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P71" t="n">
         <v>1.66</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R71" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T71" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U71" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V71" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W71" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X71" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA71" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB71" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC71" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD71" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE71" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF71" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AG71" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AH71" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AI71" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ71" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK71" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL71" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM71" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN71" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO71" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ71" t="n">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR71" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS71" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.97</v>
+        <v>6.8</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.95</v>
+        <v>6.8</v>
       </c>
       <c r="AV71" t="n">
-        <v>2.14</v>
+        <v>12</v>
       </c>
       <c r="AW71" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="AX71" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY71" t="n">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="AZ71" t="n">
-        <v>2.22</v>
+        <v>18.5</v>
       </c>
       <c r="BA71" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="BB71" t="n">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="BC71" t="n">
         <v>22</v>
       </c>
       <c r="BD71" t="n">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="BE71" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG71" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14337,13 +14337,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G72" t="n">
         <v>2.24</v>
       </c>
       <c r="H72" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I72" t="n">
         <v>4.4</v>
@@ -14352,10 +14352,10 @@
         <v>3.35</v>
       </c>
       <c r="K72" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L72" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M72" t="n">
         <v>1.09</v>
@@ -14364,10 +14364,10 @@
         <v>3</v>
       </c>
       <c r="O72" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P72" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q72" t="n">
         <v>2.42</v>
@@ -14448,59 +14448,59 @@
         <v>9.4</v>
       </c>
       <c r="AQ72" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR72" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS72" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AU72" t="n">
         <v>6.6</v>
       </c>
       <c r="AV72" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX72" t="n">
         <v>9.6</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AZ72" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA72" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB72" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC72" t="n">
         <v>21</v>
       </c>
       <c r="BD72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE72" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF72" t="n">
         <v>16</v>
       </c>
       <c r="BG72" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
         <v>44</v>
       </c>
       <c r="AM73" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN73" t="n">
         <v>34</v>
@@ -14654,7 +14654,7 @@
         <v>14</v>
       </c>
       <c r="AU73" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV73" t="n">
         <v>10.5</v>
@@ -14675,7 +14675,7 @@
         <v>30</v>
       </c>
       <c r="BB73" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC73" t="n">
         <v>34</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14728,16 +14728,16 @@
         <v>1.86</v>
       </c>
       <c r="G74" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H74" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I74" t="n">
         <v>5.3</v>
       </c>
       <c r="J74" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K74" t="n">
         <v>3.95</v>
@@ -14758,25 +14758,25 @@
         <v>1.88</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R74" t="n">
         <v>1.34</v>
       </c>
       <c r="S74" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T74" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U74" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W74" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X74" t="n">
         <v>16</v>
@@ -14791,7 +14791,7 @@
         <v>140</v>
       </c>
       <c r="AB74" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC74" t="n">
         <v>8.6</v>
@@ -14830,7 +14830,7 @@
         <v>13.5</v>
       </c>
       <c r="AO74" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP74" t="n">
         <v>12</v>
@@ -14839,10 +14839,10 @@
         <v>14.5</v>
       </c>
       <c r="AR74" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS74" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT74" t="n">
         <v>7.4</v>
@@ -14854,19 +14854,19 @@
         <v>17</v>
       </c>
       <c r="AW74" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="AX74" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY74" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ74" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA74" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB74" t="n">
         <v>17.5</v>
@@ -14878,17 +14878,17 @@
         <v>32</v>
       </c>
       <c r="BE74" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF74" t="n">
         <v>11.5</v>
       </c>
       <c r="BG74" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
         <v>18</v>
       </c>
       <c r="AE75" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF75" t="n">
         <v>16.5</v>
@@ -15060,7 +15060,7 @@
         <v>18.5</v>
       </c>
       <c r="BA75" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB75" t="n">
         <v>5.1</v>
@@ -15072,7 +15072,7 @@
         <v>5.3</v>
       </c>
       <c r="BE75" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF75" t="n">
         <v>5</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15113,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="G76" t="n">
-        <v>1.57</v>
+        <v>1000</v>
       </c>
       <c r="H76" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I76" t="n">
         <v>1000</v>
       </c>
       <c r="J76" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="K76" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15161,10 +15161,10 @@
         <v>1.01</v>
       </c>
       <c r="V76" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15501,170 +15501,170 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="G78" t="n">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="H78" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I78" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>2.8</v>
+        <v>1.02</v>
       </c>
       <c r="K78" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
       </c>
       <c r="M78" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="O78" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P78" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="R78" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>4.5</v>
+        <v>1.52</v>
       </c>
       <c r="T78" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U78" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W78" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z78" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA78" t="n">
         <v>1000</v>
       </c>
       <c r="AB78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD78" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE78" t="n">
         <v>1000</v>
       </c>
       <c r="AF78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG78" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH78" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI78" t="n">
         <v>1000</v>
       </c>
       <c r="AJ78" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK78" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL78" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM78" t="n">
         <v>1000</v>
       </c>
       <c r="AN78" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO78" t="n">
         <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AQ78" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR78" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS78" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU78" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AV78" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW78" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX78" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY78" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ78" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA78" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB78" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BC78" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BD78" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE78" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF78" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BG78" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15698,19 +15698,19 @@
         <v>1.36</v>
       </c>
       <c r="G79" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H79" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="I79" t="n">
         <v>13</v>
       </c>
       <c r="J79" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K79" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15722,13 +15722,13 @@
         <v>3.45</v>
       </c>
       <c r="O79" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P79" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R79" t="n">
         <v>1.32</v>
@@ -15737,16 +15737,16 @@
         <v>3.5</v>
       </c>
       <c r="T79" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U79" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V79" t="n">
         <v>1.08</v>
       </c>
       <c r="W79" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X79" t="n">
         <v>15.5</v>
@@ -15773,7 +15773,7 @@
         <v>1000</v>
       </c>
       <c r="AF79" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG79" t="n">
         <v>11</v>
@@ -15803,7 +15803,7 @@
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ79" t="n">
         <v>7</v>
@@ -15812,53 +15812,53 @@
         <v>8.6</v>
       </c>
       <c r="AS79" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW79" t="n">
         <v>9</v>
       </c>
-      <c r="AT79" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AX79" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ79" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA79" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB79" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC79" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BD79" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BE79" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF79" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG79" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15889,22 +15889,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H80" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J80" t="n">
         <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16083,22 +16083,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H81" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I81" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>3.3</v>
       </c>
       <c r="K81" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16107,13 +16107,13 @@
         <v>1.1</v>
       </c>
       <c r="N81" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O81" t="n">
         <v>1.41</v>
       </c>
       <c r="P81" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q81" t="n">
         <v>2.26</v>
@@ -16131,10 +16131,10 @@
         <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W81" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16277,22 +16277,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G82" t="n">
         <v>2.04</v>
       </c>
       <c r="H82" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I82" t="n">
         <v>6.2</v>
       </c>
       <c r="J82" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K82" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16301,16 +16301,16 @@
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O82" t="n">
         <v>1.35</v>
       </c>
       <c r="P82" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R82" t="n">
         <v>1.25</v>
@@ -16328,7 +16328,7 @@
         <v>1.19</v>
       </c>
       <c r="W82" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16603,7 +16603,7 @@
         <v>2.08</v>
       </c>
       <c r="AX83" t="n">
-        <v>2.06</v>
+        <v>17.5</v>
       </c>
       <c r="AY83" t="n">
         <v>1.98</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G84" t="n">
         <v>2.58</v>
@@ -16674,10 +16674,10 @@
         <v>3.35</v>
       </c>
       <c r="I84" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J84" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K84" t="n">
         <v>3.4</v>
@@ -16689,13 +16689,13 @@
         <v>1.1</v>
       </c>
       <c r="N84" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O84" t="n">
         <v>1.45</v>
       </c>
       <c r="P84" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q84" t="n">
         <v>2.32</v>
@@ -16707,13 +16707,13 @@
         <v>4.4</v>
       </c>
       <c r="T84" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U84" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V84" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W84" t="n">
         <v>1.64</v>
@@ -16725,7 +16725,7 @@
         <v>11</v>
       </c>
       <c r="Z84" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA84" t="n">
         <v>85</v>
@@ -16740,7 +16740,7 @@
         <v>15.5</v>
       </c>
       <c r="AE84" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF84" t="n">
         <v>970</v>
@@ -16758,7 +16758,7 @@
         <v>46</v>
       </c>
       <c r="AK84" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL84" t="n">
         <v>60</v>
@@ -16773,7 +16773,7 @@
         <v>70</v>
       </c>
       <c r="AP84" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ84" t="n">
         <v>9.6</v>
@@ -16782,10 +16782,10 @@
         <v>17</v>
       </c>
       <c r="AS84" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT84" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU84" t="n">
         <v>6.4</v>
@@ -16794,41 +16794,41 @@
         <v>13</v>
       </c>
       <c r="AW84" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX84" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY84" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ84" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA84" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD84" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB84" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC84" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE84" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF84" t="n">
         <v>19</v>
       </c>
       <c r="BG84" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,33 +743,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:59:57</t>
+          <t>20:32:04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1.01</v>
       </c>
       <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.01</v>
       </c>
-      <c r="H2" t="n">
-        <v>36</v>
-      </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -817,7 +817,7 @@
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>1.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -847,7 +847,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -865,69 +865,69 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>220</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>220</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>110</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-06 20:25:53</t>
+          <t>2026-03-06 22:56:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,114 +937,114 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:02:05</t>
+          <t>21:31:04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>2.32</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>10</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.49</v>
+        <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,75 +1053,75 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>110</v>
+        <v>3.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>210</v>
       </c>
       <c r="AT3" t="n">
-        <v>110</v>
+        <v>3.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.57</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>380</v>
       </c>
       <c r="AX3" t="n">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.34</v>
+        <v>85</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.34</v>
+        <v>130</v>
       </c>
       <c r="BB3" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.34</v>
+        <v>90</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.57</v>
+        <v>60</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.34</v>
+        <v>130</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.34</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-06 20:25:53</t>
+          <t>2026-03-06 22:56:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:06:34</t>
+          <t>22:01:11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mazatlan FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>17.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1169,153 +1169,153 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BD4" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S4" t="n">
-        <v>80</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="BE4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.08</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>18</v>
-      </c>
       <c r="BG4" t="n">
-        <v>14</v>
+        <v>1.09</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-06 20:25:53</t>
+          <t>2026-03-06 22:56:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,960 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:15</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.46</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>2.94</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK5" t="n">
         <v>25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>44</v>
       </c>
-      <c r="BE5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>90</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-06 20:25:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Deportes Concepcion</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Nublense</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:25:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Delfin</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:25:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mazatlan FC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Leon</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:25:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:25:53</t>
+          <t>2026-03-06 22:56:49</t>
         </is>
       </c>
     </row>
